--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484239_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484239_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9638</v>
+        <v>8.210900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8605</v>
+        <v>7.3255</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1033</v>
+        <v>0.8854</v>
       </c>
       <c r="G2" t="n">
         <v>7.6544</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2509</v>
+        <v>0.498</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1499</v>
+        <v>-0.6849</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4008</v>
+        <v>1.1829</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9331</v>
+        <v>7.5482</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5445</v>
+        <v>3.9466</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3887</v>
+        <v>3.6017</v>
       </c>
       <c r="G3" t="n">
-        <v>6.7861</v>
+        <v>5.1459</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8491</v>
+        <v>0.6813</v>
       </c>
       <c r="I3" t="n">
-        <v>4.937</v>
+        <v>4.4647</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5045</v>
+        <v>3.8173</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9713</v>
+        <v>0.431</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5331</v>
+        <v>3.3863</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7184</v>
+        <v>1.3286</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1223</v>
+        <v>0.2502</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4039</v>
+        <v>1.0784</v>
       </c>
       <c r="P3" t="n">
         <v>0.586</v>
@@ -688,28 +688,28 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3341</v>
+        <v>0.8749</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0167</v>
+        <v>-0.1127</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3174</v>
+        <v>0.9876</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7731</v>
+        <v>0.9414</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7731</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9235</v>
+        <v>6.6788</v>
       </c>
       <c r="E4" t="n">
-        <v>3.886</v>
+        <v>5.9983</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0374</v>
+        <v>0.6805</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1459</v>
+        <v>6.7861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6813</v>
+        <v>1.8491</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4647</v>
+        <v>4.937</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8173</v>
+        <v>7.5045</v>
       </c>
       <c r="K4" t="n">
-        <v>0.431</v>
+        <v>2.9713</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3863</v>
+        <v>4.5331</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3286</v>
+        <v>-0.7184</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2502</v>
+        <v>-1.1223</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0784</v>
+        <v>0.4039</v>
       </c>
       <c r="P4" t="n">
         <v>0.586</v>
@@ -766,28 +766,28 @@
         <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2501</v>
+        <v>1.0798</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1732</v>
+        <v>-0.5295</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4233</v>
+        <v>1.6093</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9414</v>
+        <v>-1.7731</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2115</v>
+        <v>1.9592</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7194</v>
+        <v>0.7696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4921</v>
+        <v>1.1897</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0911</v>
+        <v>4.0128</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1614</v>
+        <v>1.6383</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2525</v>
+        <v>2.3745</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5667</v>
+        <v>2.3396</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5513</v>
+        <v>1.0438</v>
       </c>
       <c r="L5" t="n">
-        <v>2.118</v>
+        <v>1.2959</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5243</v>
+        <v>1.6731</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3899</v>
+        <v>0.5946</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1344</v>
+        <v>1.0786</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4209</v>
+        <v>-0.0303</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1294</v>
+        <v>-0.2613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2916</v>
+        <v>0.231</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4959</v>
+        <v>-1.8279</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X5" t="n">
         <v>-1.4959</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1129</v>
+        <v>1.3477</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3046</v>
+        <v>0.7194</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8084</v>
+        <v>0.6282</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0128</v>
+        <v>2.0911</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6383</v>
+        <v>-0.1614</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3745</v>
+        <v>2.2525</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3396</v>
+        <v>1.5667</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0438</v>
+        <v>-0.5513</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2959</v>
+        <v>2.118</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6731</v>
+        <v>0.5243</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5946</v>
+        <v>0.3899</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0786</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.1294</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1503</v>
+        <v>0.4277</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.4959</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5576</v>
+        <v>1.1139</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6125</v>
+        <v>-0.4102</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.5241</v>
       </c>
       <c r="G7" t="n">
         <v>3.7516</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5178</v>
+        <v>0.0385</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0336</v>
+        <v>0.3205</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3321</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4815</v>
+        <v>0.6727</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2656</v>
+        <v>-0.3468</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7471</v>
+        <v>1.0195</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8589</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.187</v>
+        <v>0.0042</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.839</v>
+        <v>-0.9202</v>
       </c>
       <c r="U8" t="n">
-        <v>0.652</v>
+        <v>0.9243</v>
       </c>
       <c r="V8" t="n">
         <v>0.9414</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3472</v>
+        <v>-0.24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3821</v>
+        <v>0.5437</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6719000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1711</v>
+        <v>-0.064</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7367</v>
+        <v>0.6822</v>
       </c>
       <c r="V9" t="n">
         <v>0.8865</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.07</v>
+        <v>-1.0095</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.121</v>
+        <v>-0.0605</v>
       </c>
       <c r="F10" t="n">
         <v>-0.949</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.121</v>
+        <v>-0.0605</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>-0.0605</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2092</v>
+        <v>-1.1021</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2844</v>
+        <v>-2.1228</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0752</v>
+        <v>1.0207</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1729</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0363</v>
+        <v>0.0709</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3026</v>
+        <v>-0.141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2663</v>
+        <v>0.2118</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5106</v>
+        <v>-2.5277</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3296</v>
+        <v>-1.6735</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.181</v>
+        <v>-0.8542</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7292</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0902</v>
+        <v>-0.1073</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1732</v>
+        <v>-0.5172</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.4099</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.0469</v>
+        <v>22.6521</v>
       </c>
       <c r="E13" t="n">
-        <v>14.084</v>
+        <v>14.6893</v>
       </c>
       <c r="F13" t="n">
-        <v>7.9629</v>
+        <v>7.962800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>24.2786</v>
@@ -1468,13 +1468,13 @@
         <v>10.7437</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2561</v>
+        <v>2.8613</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7311</v>
+        <v>-4.1261</v>
       </c>
       <c r="U13" t="n">
-        <v>6.9873</v>
+        <v>6.987200000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.4876</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.967</v>
+        <v>0.8969</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2032</v>
+        <v>3.0658</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2362</v>
+        <v>-2.1689</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.1484</v>
+        <v>-0.9754</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4894</v>
+        <v>1.6685</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.6378</v>
+        <v>-2.6439</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4307</v>
+        <v>3.6448</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4254</v>
+        <v>3.0507</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.9947</v>
+        <v>0.5942</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5791</v>
+        <v>-4.6202</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.936</v>
+        <v>-1.3822</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.6431</v>
+        <v>-3.238</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3927</v>
+        <v>-0.3583</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.528</v>
+        <v>-1.2702</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9207</v>
+        <v>0.9119</v>
       </c>
       <c r="V14" t="n">
-        <v>2.16</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5663</v>
+        <v>-0.2661</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7624</v>
+        <v>1.5966</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1961</v>
+        <v>-1.8626</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9754</v>
+        <v>-4.1484</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6685</v>
+        <v>1.4894</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6439</v>
+        <v>-5.6378</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6448</v>
+        <v>1.4307</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0507</v>
+        <v>3.4254</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5942</v>
+        <v>-1.9947</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.6202</v>
+        <v>-5.5791</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3822</v>
+        <v>-1.936</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.238</v>
+        <v>-3.6431</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6889</v>
+        <v>0.1596</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5736</v>
+        <v>-1.1347</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8847</v>
+        <v>1.2942</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>2.16</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.8302</v>
+        <v>-2.4646</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8177</v>
+        <v>-1.6155</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0125</v>
+        <v>-0.8491</v>
       </c>
       <c r="G16" t="n">
         <v>-2.6365</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.4141</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5447</v>
+        <v>-0.3425</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.235</v>
+        <v>-0.0716</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1006</v>
+        <v>-4.1043</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.996</v>
+        <v>-1.2993</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1046</v>
+        <v>-2.805</v>
       </c>
       <c r="G17" t="n">
         <v>-3.5425</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5265</v>
+        <v>-0.5303</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7784</v>
+        <v>-1.0818</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2519</v>
+        <v>0.5515</v>
       </c>
       <c r="V17" t="n">
         <v>0.5545</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.639</v>
+        <v>-4.145</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5794</v>
+        <v>-2.2761</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0596</v>
+        <v>-1.8689</v>
       </c>
       <c r="G18" t="n">
         <v>-3.803</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0779</v>
+        <v>-0.5839</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0289</v>
+        <v>-0.7255</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.049</v>
+        <v>0.1416</v>
       </c>
       <c r="V18" t="n">
         <v>1.2186</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.804</v>
+        <v>-5.8408</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7723</v>
+        <v>-4.561</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0317</v>
+        <v>-1.2798</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.4043</v>
+        <v>-3.7684</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5204</v>
+        <v>-1.4206</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.8839</v>
+        <v>-2.3478</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1748</v>
+        <v>-0.3668</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4157</v>
+        <v>-0.4477</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2408</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.5791</v>
+        <v>-3.4016</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.936</v>
+        <v>-0.9729</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.6431</v>
+        <v>-2.4287</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0225</v>
+        <v>-0.2325</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2626</v>
+        <v>-1.0687</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2852</v>
+        <v>0.8363</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.2065</v>
+        <v>-6.123</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7632</v>
+        <v>-2.8734</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4432</v>
+        <v>-3.2496</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7684</v>
+        <v>-5.4043</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4206</v>
+        <v>-1.5204</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3478</v>
+        <v>-3.8839</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3668</v>
+        <v>0.1748</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4477</v>
+        <v>0.4157</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-0.2408</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4016</v>
+        <v>-5.5791</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9729</v>
+        <v>-1.936</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.4287</v>
+        <v>-3.6431</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5981</v>
+        <v>-0.2965</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.271</v>
+        <v>-1.3637</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6728</v>
+        <v>1.0673</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-22.047</v>
+        <v>-22.0469</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.963000000000001</v>
+        <v>-7.9629</v>
       </c>
       <c r="F21" t="n">
         <v>-14.0839</v>
@@ -2074,7 +2074,7 @@
         <v>-2.6925</v>
       </c>
       <c r="M21" t="n">
-        <v>-27.8956</v>
+        <v>-27.89560000000001</v>
       </c>
       <c r="N21" t="n">
         <v>-9.680099999999999</v>
@@ -2083,7 +2083,7 @@
         <v>-18.2154</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q21" t="n">
         <v>-10.7438</v>
@@ -2092,13 +2092,13 @@
         <v>10.7438</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2559</v>
+        <v>-2.256</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.9872</v>
+        <v>-6.9871</v>
       </c>
       <c r="U21" t="n">
-        <v>4.7313</v>
+        <v>4.731199999999999</v>
       </c>
       <c r="V21" t="n">
         <v>4.4876</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484239_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484239_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6727</v>
+        <v>0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3468</v>
+        <v>0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0195</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8589</v>
+        <v>0.614</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6838</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1751</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6636</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1077</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4441</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7915</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9202</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9243</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.24</v>
+        <v>0.0587</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5437</v>
+        <v>-0.9607</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7838000000000001</v>
+        <v>1.0195</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-1.4729</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4674</v>
+        <v>-1.2978</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7955</v>
+        <v>-0.1751</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3801</v>
+        <v>0.0496</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0447</v>
+        <v>0.4937</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3354</v>
+        <v>-0.4441</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.052</v>
+        <v>-1.5225</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5121</v>
+        <v>-1.7915</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>0.269</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.064</v>
+        <v>0.0042</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7462</v>
+        <v>-0.9202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6822</v>
+        <v>0.9243</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8865</v>
+        <v>0.9414</v>
       </c>
       <c r="W9" t="n">
         <v>0.8865</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MAS CARDONA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0095</v>
+        <v>-0.24</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0605</v>
+        <v>0.5437</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.949</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2696</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.4674</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2696</v>
+        <v>0.7955</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.3801</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0447</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3354</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2696</v>
+        <v>-2.052</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.5121</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2696</v>
+        <v>-0.5399</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0605</v>
+        <v>-0.064</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0605</v>
+        <v>-0.7462</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.6822</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>O. MAS CARDONA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,41 +1317,41 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1021</v>
+        <v>-1.0095</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1228</v>
+        <v>-0.0605</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0207</v>
+        <v>-0.949</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1729</v>
+        <v>0.2696</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4045</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7685</v>
+        <v>0.2696</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9818</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8089</v>
+        <v>0.2696</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.2696</v>
       </c>
-      <c r="O11" t="n">
-        <v>0.5393</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1312,28 +1362,33 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0709</v>
+        <v>-0.0605</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.141</v>
+        <v>-0.0605</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2118</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5277</v>
+        <v>-1.1021</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6735</v>
+        <v>-2.1228</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8542</v>
+        <v>1.0207</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7292</v>
+        <v>-1.1729</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3676</v>
+        <v>-0.4045</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3616</v>
+        <v>-0.7685</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1564</v>
+        <v>-1.9818</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4694</v>
+        <v>-0.6741</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6869</v>
+        <v>-1.3077</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5729</v>
+        <v>0.8089</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8982</v>
+        <v>0.2696</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6747</v>
+        <v>0.5393</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1073</v>
+        <v>0.0709</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5172</v>
+        <v>-0.141</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4099</v>
+        <v>0.2118</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.6521</v>
+        <v>-2.5277</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6893</v>
+        <v>-1.6735</v>
       </c>
       <c r="F13" t="n">
-        <v>7.962800000000001</v>
+        <v>-0.8542</v>
       </c>
       <c r="G13" t="n">
-        <v>24.2786</v>
+        <v>-2.7292</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3705</v>
+        <v>-1.3676</v>
       </c>
       <c r="I13" t="n">
-        <v>20.908</v>
+        <v>-1.3616</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8956</v>
+        <v>-1.1564</v>
       </c>
       <c r="K13" t="n">
-        <v>9.680099999999999</v>
+        <v>-0.4694</v>
       </c>
       <c r="L13" t="n">
-        <v>18.2156</v>
+        <v>-0.6869</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6173</v>
+        <v>-1.5729</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.309600000000001</v>
+        <v>-0.8982</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6924</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0001000000000001</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.7438</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>10.7437</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8613</v>
+        <v>-0.1073</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1261</v>
+        <v>-0.5172</v>
       </c>
       <c r="U13" t="n">
-        <v>6.987200000000001</v>
+        <v>0.4099</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.4876</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6632</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.150899999999999</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8969</v>
+        <v>22.6521</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0658</v>
+        <v>14.6894</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1689</v>
+        <v>7.962800000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9754</v>
+        <v>24.2786</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6685</v>
+        <v>3.3705</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.6439</v>
+        <v>20.908</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6448</v>
+        <v>27.8956</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0507</v>
+        <v>9.680099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5942</v>
+        <v>18.2156</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.6202</v>
+        <v>-3.6173</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3822</v>
+        <v>-6.309600000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.238</v>
+        <v>2.6924</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9534</v>
+        <v>-0.0001000000000003221</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-10.7438</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>10.7437</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3583</v>
+        <v>2.8613</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2702</v>
+        <v>-4.1261</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9119</v>
+        <v>6.9872</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-4.4876</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>1.6632</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
-      </c>
+        <v>-6.150899999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2661</v>
+        <v>0.8969</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5966</v>
+        <v>3.0658</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8626</v>
+        <v>-2.1689</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.1484</v>
+        <v>-0.9754</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4894</v>
+        <v>1.6685</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.6378</v>
+        <v>-2.6439</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4307</v>
+        <v>3.6448</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4254</v>
+        <v>3.0507</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9947</v>
+        <v>0.5942</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5791</v>
+        <v>-4.6202</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.936</v>
+        <v>-1.3822</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.6431</v>
+        <v>-3.238</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1596</v>
+        <v>-0.3583</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1347</v>
+        <v>-1.2702</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2942</v>
+        <v>0.9119</v>
       </c>
       <c r="V15" t="n">
-        <v>2.16</v>
+        <v>0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4646</v>
+        <v>-0.2661</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6155</v>
+        <v>1.5966</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8491</v>
+        <v>-1.8626</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6365</v>
+        <v>-4.1484</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1665</v>
+        <v>1.4894</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.47</v>
+        <v>-5.6378</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.273</v>
+        <v>1.4307</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6127</v>
+        <v>3.4254</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6603</v>
+        <v>-1.9947</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3636</v>
+        <v>-5.5791</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5538</v>
+        <v>-1.936</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8097</v>
+        <v>-3.6431</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4141</v>
+        <v>0.1596</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3425</v>
+        <v>-1.1347</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0716</v>
+        <v>1.2942</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1043</v>
+        <v>-2.4646</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2993</v>
+        <v>-1.6155</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.805</v>
+        <v>-0.8491</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.5425</v>
+        <v>-2.6365</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5048</v>
+        <v>-1.1665</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0377</v>
+        <v>-1.47</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8223</v>
+        <v>-1.273</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7009</v>
+        <v>-0.6127</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>-0.6603</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.3648</v>
+        <v>-1.3636</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2057</v>
+        <v>-0.5538</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1591</v>
+        <v>-0.8097</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5303</v>
+        <v>-0.4141</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0818</v>
+        <v>-0.3425</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5515</v>
+        <v>-0.0716</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.145</v>
+        <v>-4.1043</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2761</v>
+        <v>-1.2993</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8689</v>
+        <v>-2.805</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.803</v>
+        <v>-3.5425</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9161</v>
+        <v>-1.5048</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8869</v>
+        <v>-2.0377</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8158</v>
+        <v>0.8223</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2226</v>
+        <v>0.7009</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9872</v>
+        <v>-4.3648</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6935</v>
+        <v>-2.2057</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2937</v>
+        <v>-2.1591</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5839</v>
+        <v>-0.5303</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7255</v>
+        <v>-1.0818</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1416</v>
+        <v>0.5515</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>1.1089</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.8408</v>
+        <v>-4.145</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.561</v>
+        <v>-2.2761</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2798</v>
+        <v>-1.8689</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7684</v>
+        <v>-3.803</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4206</v>
+        <v>-0.9161</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3478</v>
+        <v>-2.8869</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3668</v>
+        <v>-0.8158</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4477</v>
+        <v>-0.2226</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4016</v>
+        <v>-2.9872</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9729</v>
+        <v>-0.6935</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4287</v>
+        <v>-2.2937</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2325</v>
+        <v>-0.5839</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0687</v>
+        <v>-0.7255</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8363</v>
+        <v>0.1416</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.123</v>
+        <v>-5.8408</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8734</v>
+        <v>-4.561</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2496</v>
+        <v>-1.2798</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.4043</v>
+        <v>-3.7684</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5204</v>
+        <v>-1.4206</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.8839</v>
+        <v>-2.3478</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1748</v>
+        <v>-0.3668</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4157</v>
+        <v>-0.4477</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2408</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.5791</v>
+        <v>-3.4016</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.936</v>
+        <v>-0.9729</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.6431</v>
+        <v>-2.4287</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2965</v>
+        <v>-0.2325</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3637</v>
+        <v>-1.0687</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0673</v>
+        <v>0.8363</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,152 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-6.123</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.8734</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3.2496</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.4043</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.5204</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-3.8839</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.2408</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-5.5791</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.936</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-3.6431</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.2965</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.3637</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.0673</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484239_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>-22.0469</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>-7.9629</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>-14.0839</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>-24.2785</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>-3.3705</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>-20.908</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>3.617</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>6.309699999999999</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>-2.6925</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>-27.89560000000001</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>-9.680099999999999</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>-18.2154</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>1.110223024625157e-16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>-10.7438</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>10.7438</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>-2.256</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>-6.9871</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>4.731199999999999</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>4.4876</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W22" t="n">
         <v>6.150899999999999</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>-1.6633</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
